--- a/artfynd/A 8725-2025 artfynd.xlsx
+++ b/artfynd/A 8725-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123049204</v>
+        <v>123129052</v>
       </c>
       <c r="B2" t="n">
         <v>57494</v>
@@ -710,29 +710,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björke Tynne, Gtl</t>
@@ -769,12 +757,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 8725-2025 artfynd.xlsx
+++ b/artfynd/A 8725-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123129052</v>
+        <v>123049204</v>
       </c>
       <c r="B2" t="n">
         <v>57494</v>
@@ -710,17 +710,29 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björke Tynne, Gtl</t>
@@ -757,22 +769,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 8725-2025 artfynd.xlsx
+++ b/artfynd/A 8725-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123129052</v>
+        <v>123049204</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,17 +710,29 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björke Tynne, Gtl</t>
@@ -757,22 +769,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 8725-2025 artfynd.xlsx
+++ b/artfynd/A 8725-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123049204</v>
+        <v>123129052</v>
       </c>
       <c r="B2" t="n">
         <v>57497</v>
@@ -710,29 +710,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björke Tynne, Gtl</t>
@@ -769,12 +757,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 8725-2025 artfynd.xlsx
+++ b/artfynd/A 8725-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123129052</v>
+        <v>123049204</v>
       </c>
       <c r="B2" t="n">
         <v>57497</v>
@@ -710,17 +710,29 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björke Tynne, Gtl</t>
@@ -757,22 +769,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 8725-2025 artfynd.xlsx
+++ b/artfynd/A 8725-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123129052</v>
+        <v>123049204</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,17 +710,29 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björke Tynne, Gtl</t>
@@ -757,22 +769,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 8725-2025 artfynd.xlsx
+++ b/artfynd/A 8725-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123049204</v>
+        <v>123129052</v>
       </c>
       <c r="B2" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,29 +710,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björke Tynne, Gtl</t>
@@ -769,12 +757,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 8725-2025 artfynd.xlsx
+++ b/artfynd/A 8725-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123129052</v>
+        <v>123049204</v>
       </c>
       <c r="B2" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,17 +710,29 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björke Tynne, Gtl</t>
@@ -757,22 +769,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
